--- a/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-procedure.xlsx
+++ b/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-procedure.xlsx
@@ -680,7 +680,7 @@
     <t>行われた具体的な手順。手技の正確な性質がコード化できない場合はテキストを使用する（例：「腹腔鏡下虫垂切除術」）</t>
   </si>
   <si>
-    <t>すべての用語の使用がこの一般的なパターンに当てはまるわけではない。場合によっては、モデルはCodeableConceptを使用せず、Codingを直接使用し、テキスト、コーディング、翻訳、要素間の関係や事前・事後の調整を管理するための独自の構造を提供すべきである。</t>
+    <t>すべての用語の使用がこの一般的なパターンに当てはまるわけではない。場合によっては、モデルはCodeableConceptを使用せず、`Coding`を直接使用し、テキスト、`Coding`、翻訳、要素間の関係や事前・事後の調整を管理するための独自の構造を提供すべきである。</t>
   </si>
   <si>
     <t>0..1主に叙述(Narative)のみのリソースを説明する。 / 0..1 to account for primarily narrative only resources.</t>
@@ -1272,7 +1272,7 @@
     <t>プロシジャーへの実施者の関与のタイプを区別する。たとえば、外科医、麻酔科医、内視鏡医。</t>
   </si>
   <si>
-    <t>すべての用語の使用がこの一般的なパターンに当てはまるわけではない。場合によっては、モデルはCodeableConceptを使用せず、Codingを直接使用し、テキスト、コーディング、翻訳、要素間の関係や事前・事後の調整を管理するための独自の構造を提供するべきである。  
+    <t>すべての用語の使用がこの一般的なパターンに当てはまるわけではない。場合によっては、モデルはCodeableConceptを使用せず、`Coding`を直接使用し、テキスト、`Coding`、翻訳、要素間の関係や事前・事後の調整を管理するための独自の構造を提供するべきである。  
  【JP Core仕様】当面利用しない。</t>
   </si>
   <si>
@@ -1544,7 +1544,7 @@
   </si>
   <si>
     <t>構造化された注釈（アノテーション）を持たないシステムの場合、作成者や時間なしで単一の注釈を簡単に伝達できる。情報を変更する可能性があるため、この要素をナラティブに含める必要がある場合がある。   
-*注釈は、計算機処理れきる「変更」情報を伝達するために使用されるべきではない*。 （ユーザの行動を強制することはほとんど不可能であるため、これはSHOULDとする）。</t>
+*注釈は、計算機処理れきる「変更」情報を伝達するために使用されるべきではない*。 （ユーザーの行動を強制することはほとんど不可能であるため、これはSHOULDとする）。</t>
   </si>
   <si>
     <t>Event.note</t>
